--- a/release_1_0_0/data/files/output/ml/eval_ml_loo.xlsx
+++ b/release_1_0_0/data/files/output/ml/eval_ml_loo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,92 +431,102 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>eval_biased</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>taux_conversion_reel</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>taux_conversion_predit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>taux_conversion_baseline</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>conversion_scale</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>montant_ventes_par_mois_reel</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>montant_ventes_par_mois_predit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>montant_ventes_par_mois_erreur</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>montant_ventes_par_mois_erreur_absolue</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>pred_sim_v2__montant_ventes_par_mois</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>montant_marge_par_mois_reel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>montant_marge_par_mois_predit</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>montant_marge_par_mois_erreur</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>montant_marge_par_mois_erreur_absolue</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>pred_sim_v2__montant_marge_par_mois</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>montant_marge_selon_coef_par_mois_reel</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>montant_marge_selon_coef_par_mois_predit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>montant_marge_selon_coef_par_mois_erreur</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>montant_marge_selon_coef_par_mois_erreur_absolue</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>pred_sim_v2__montant_marge_selon_coef_par_mois</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>pred_xgboost__montant_ventes_par_mois</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pred_xgboost__montant_marge_par_mois</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pred_xgboost__montant_marge_selon_coef_par_mois</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>montant_ventes_par_mois_reel</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>montant_ventes_par_mois_predit</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>montant_ventes_par_mois_erreur</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>montant_ventes_par_mois_erreur_absolue</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>montant_marge_par_mois_reel</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>montant_marge_par_mois_predit</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>montant_marge_par_mois_erreur</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>montant_marge_par_mois_erreur_absolue</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>montant_marge_selon_coef_par_mois_reel</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>montant_marge_selon_coef_par_mois_predit</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>montant_marge_selon_coef_par_mois_erreur</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>montant_marge_selon_coef_par_mois_erreur_absolue</t>
         </is>
       </c>
     </row>
@@ -531,59 +541,65 @@
           <t>connected</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>10738.49924213908</v>
+      <c r="C2" t="b">
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5738.392028833131</v>
+        <v>0.04412064830175411</v>
       </c>
       <c r="E2" t="n">
-        <v>5550.20024950137</v>
+        <v>0.0719614252448082</v>
       </c>
       <c r="F2" t="n">
-        <v>1165.529052734375</v>
+        <v>0.09885716389404486</v>
       </c>
       <c r="G2" t="n">
-        <v>509.4608459472656</v>
+        <v>0.7279333374558112</v>
       </c>
       <c r="H2" t="n">
-        <v>599.8309936523438</v>
+        <v>3432.306971428518</v>
       </c>
       <c r="I2" t="n">
-        <v>3432.306971428518</v>
+        <v>8417.752032902474</v>
       </c>
       <c r="J2" t="n">
-        <v>1258.400268554688</v>
+        <v>4985.445061473956</v>
       </c>
       <c r="K2" t="n">
-        <v>-2173.90670287383</v>
+        <v>4985.445061473956</v>
       </c>
       <c r="L2" t="n">
-        <v>2173.90670287383</v>
+        <v>11563.90509922685</v>
       </c>
       <c r="M2" t="n">
         <v>2214.074874999865</v>
       </c>
       <c r="N2" t="n">
-        <v>652.7255249023438</v>
+        <v>4410.475510040579</v>
       </c>
       <c r="O2" t="n">
-        <v>-1561.349350097521</v>
+        <v>2196.400635040714</v>
       </c>
       <c r="P2" t="n">
-        <v>1561.349350097521</v>
+        <v>2196.400635040714</v>
       </c>
       <c r="Q2" t="n">
+        <v>6058.900290863949</v>
+      </c>
+      <c r="R2" t="n">
         <v>1977.989434346401</v>
       </c>
-      <c r="R2" t="n">
-        <v>619.6922607421875</v>
-      </c>
       <c r="S2" t="n">
-        <v>-1358.297173604214</v>
+        <v>4417.128453020146</v>
       </c>
       <c r="T2" t="n">
-        <v>1358.297173604214</v>
+        <v>2439.139018673745</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2439.139018673745</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6068.039785701236</v>
       </c>
     </row>
     <row r="3">
@@ -597,59 +613,65 @@
           <t>simply</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1993.296293710695</v>
+      <c r="C3" t="b">
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>947.8373290228487</v>
+        <v>0.03407324952031283</v>
       </c>
       <c r="E3" t="n">
-        <v>1115.053900402543</v>
+        <v>0.03405093401670456</v>
       </c>
       <c r="F3" t="n">
-        <v>1524.940551757812</v>
+        <v>0.03067157265002578</v>
       </c>
       <c r="G3" t="n">
-        <v>819.1807250976562</v>
+        <v>1.110178940129304</v>
       </c>
       <c r="H3" t="n">
-        <v>719.0278930664062</v>
+        <v>570.2660606060817</v>
       </c>
       <c r="I3" t="n">
-        <v>570.2660606060817</v>
+        <v>708.9100951377798</v>
       </c>
       <c r="J3" t="n">
-        <v>2239.112060546875</v>
+        <v>138.644034531698</v>
       </c>
       <c r="K3" t="n">
-        <v>1668.845999940793</v>
+        <v>138.644034531698</v>
       </c>
       <c r="L3" t="n">
-        <v>1668.845999940793</v>
+        <v>638.5548036564379</v>
       </c>
       <c r="M3" t="n">
         <v>233.321212121201</v>
       </c>
       <c r="N3" t="n">
-        <v>1333.253173828125</v>
+        <v>288.7385163979222</v>
       </c>
       <c r="O3" t="n">
-        <v>1099.931961706924</v>
+        <v>55.41730427672121</v>
       </c>
       <c r="P3" t="n">
-        <v>1099.931961706924</v>
+        <v>55.41730427672121</v>
       </c>
       <c r="Q3" t="n">
+        <v>260.0828622855092</v>
+      </c>
+      <c r="R3" t="n">
         <v>248.7434418642236</v>
       </c>
-      <c r="R3" t="n">
-        <v>1218.91650390625</v>
-      </c>
       <c r="S3" t="n">
-        <v>970.1730620420263</v>
+        <v>305.1609112814566</v>
       </c>
       <c r="T3" t="n">
-        <v>970.1730620420263</v>
+        <v>56.41746941723298</v>
+      </c>
+      <c r="U3" t="n">
+        <v>56.41746941723298</v>
+      </c>
+      <c r="V3" t="n">
+        <v>274.8754279611125</v>
       </c>
     </row>
     <row r="4">
@@ -663,65 +685,71 @@
           <t>connected</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>9949.347210553828</v>
+      <c r="C4" t="b">
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6471.286683364962</v>
+        <v>0.107751341483961</v>
       </c>
       <c r="E4" t="n">
-        <v>5735.546625177109</v>
+        <v>0.044735137373209</v>
       </c>
       <c r="F4" t="n">
-        <v>2985.447998046875</v>
+        <v>0.0711871475801257</v>
       </c>
       <c r="G4" t="n">
-        <v>1910.128662109375</v>
+        <v>0.6284159275079357</v>
       </c>
       <c r="H4" t="n">
-        <v>1734.935913085938</v>
+        <v>17096.63041667935</v>
       </c>
       <c r="I4" t="n">
-        <v>17096.63041667935</v>
+        <v>8715.780559704761</v>
       </c>
       <c r="J4" t="n">
-        <v>2212.413818359375</v>
+        <v>-8380.849856974592</v>
       </c>
       <c r="K4" t="n">
-        <v>-14884.21659831998</v>
+        <v>8380.849856974592</v>
       </c>
       <c r="L4" t="n">
-        <v>14884.21659831998</v>
+        <v>13869.445661997</v>
       </c>
       <c r="M4" t="n">
         <v>9167.626249997114</v>
       </c>
       <c r="N4" t="n">
-        <v>1312.976806640625</v>
+        <v>4883.449008895345</v>
       </c>
       <c r="O4" t="n">
-        <v>-7854.649443356489</v>
+        <v>-4284.177241101769</v>
       </c>
       <c r="P4" t="n">
-        <v>7854.649443356489</v>
+        <v>4284.177241101769</v>
       </c>
       <c r="Q4" t="n">
+        <v>7771.045887174265</v>
+      </c>
+      <c r="R4" t="n">
         <v>8864.534661573482</v>
       </c>
-      <c r="R4" t="n">
-        <v>1196.107543945312</v>
-      </c>
       <c r="S4" t="n">
-        <v>-7668.427117628169</v>
+        <v>4948.110586258861</v>
       </c>
       <c r="T4" t="n">
-        <v>7668.427117628169</v>
+        <v>-3916.42407531462</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3916.42407531462</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7873.942033712021</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H6188</t>
+          <t>HB5I0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -729,191 +757,137 @@
           <t>liberty</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1515.226734659087</v>
+      <c r="C5" t="b">
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>838.0128820978642</v>
+        <v>0.01104139660255675</v>
       </c>
       <c r="E5" t="n">
-        <v>691.3281133614805</v>
+        <v>0.01098483242094517</v>
       </c>
       <c r="F5" t="n">
-        <v>2001.965698242188</v>
+        <v>0.009647482529509114</v>
       </c>
       <c r="G5" t="n">
-        <v>1421.482055664062</v>
+        <v>1.138621644283413</v>
       </c>
       <c r="H5" t="n">
-        <v>1238.922729492188</v>
+        <v>1766.508730769235</v>
       </c>
       <c r="I5" t="n">
-        <v>1438.426056822751</v>
+        <v>2272.354353910516</v>
       </c>
       <c r="J5" t="n">
-        <v>7431.8154296875</v>
+        <v>505.8456231412815</v>
       </c>
       <c r="K5" t="n">
-        <v>5993.389372864749</v>
+        <v>505.8456231412815</v>
       </c>
       <c r="L5" t="n">
-        <v>5993.389372864749</v>
+        <v>1995.706269346929</v>
       </c>
       <c r="M5" t="n">
-        <v>750.5261190476397</v>
+        <v>974.3293076923151</v>
       </c>
       <c r="N5" t="n">
-        <v>4118.6767578125</v>
+        <v>1245.17751440043</v>
       </c>
       <c r="O5" t="n">
-        <v>3368.150638764861</v>
+        <v>270.848206708115</v>
       </c>
       <c r="P5" t="n">
-        <v>3368.150638764861</v>
+        <v>270.848206708115</v>
       </c>
       <c r="Q5" t="n">
-        <v>795.1738730737154</v>
+        <v>1093.583211466244</v>
       </c>
       <c r="R5" t="n">
-        <v>3885.894287109375</v>
+        <v>815.1594794547862</v>
       </c>
       <c r="S5" t="n">
-        <v>3090.72041403566</v>
+        <v>1092.836684164202</v>
       </c>
       <c r="T5" t="n">
-        <v>3090.72041403566</v>
+        <v>277.6772047094159</v>
+      </c>
+      <c r="U5" t="n">
+        <v>277.6772047094159</v>
+      </c>
+      <c r="V5" t="n">
+        <v>959.7891359706011</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HB5I0</t>
+          <t>HB6A3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>liberty</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2175.113223112842</v>
+          <t>connected</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1150.076693968492</v>
+        <v>0.1160233891551693</v>
       </c>
       <c r="E6" t="n">
-        <v>1202.322496184466</v>
+        <v>0.03781047090888023</v>
       </c>
       <c r="F6" t="n">
-        <v>6278.04248046875</v>
+        <v>0.06723040242611222</v>
       </c>
       <c r="G6" t="n">
-        <v>3484.25439453125</v>
+        <v>0.562401377121531</v>
       </c>
       <c r="H6" t="n">
-        <v>3327.590087890625</v>
+        <v>1085.428421052641</v>
       </c>
       <c r="I6" t="n">
-        <v>1766.508730769235</v>
+        <v>367.3626993242375</v>
       </c>
       <c r="J6" t="n">
-        <v>7322.45458984375</v>
+        <v>-718.0657217284032</v>
       </c>
       <c r="K6" t="n">
-        <v>5555.945859074515</v>
+        <v>718.0657217284032</v>
       </c>
       <c r="L6" t="n">
-        <v>5555.945859074515</v>
+        <v>653.2037691736537</v>
       </c>
       <c r="M6" t="n">
-        <v>974.3293076923151</v>
+        <v>522.3989473684123</v>
       </c>
       <c r="N6" t="n">
-        <v>4044.07568359375</v>
+        <v>214.2013301940715</v>
       </c>
       <c r="O6" t="n">
-        <v>3069.746375901435</v>
+        <v>-308.1976171743408</v>
       </c>
       <c r="P6" t="n">
-        <v>3069.746375901435</v>
+        <v>308.1976171743408</v>
       </c>
       <c r="Q6" t="n">
-        <v>815.1594794547862</v>
+        <v>380.8691424092727</v>
       </c>
       <c r="R6" t="n">
-        <v>3879.232421875</v>
+        <v>607.1911078395337</v>
       </c>
       <c r="S6" t="n">
-        <v>3064.072942420214</v>
+        <v>198.7681261876786</v>
       </c>
       <c r="T6" t="n">
-        <v>3064.072942420214</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HB6A3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>simply</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>422.4384616734756</v>
-      </c>
-      <c r="D7" t="n">
-        <v>171.714378819114</v>
-      </c>
-      <c r="E7" t="n">
-        <v>180.006045991362</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6185.234375</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3426.2119140625</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3273.36328125</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1085.428421052641</v>
-      </c>
-      <c r="J7" t="n">
-        <v>7322.45458984375</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6237.02616879111</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6237.02616879111</v>
-      </c>
-      <c r="M7" t="n">
-        <v>522.3989473684123</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4044.07568359375</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3521.676736225338</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3521.676736225338</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>607.1911078395337</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3879.232421875</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3272.041314035466</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3272.041314035466</v>
+        <v>-408.4229816518551</v>
+      </c>
+      <c r="U6" t="n">
+        <v>408.4229816518551</v>
+      </c>
+      <c r="V6" t="n">
+        <v>353.4275239598608</v>
       </c>
     </row>
   </sheetData>
@@ -979,19 +953,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6085.555116977496</v>
+        <v>2945.770059569986</v>
       </c>
       <c r="E2" t="n">
-        <v>7469.276705990821</v>
+        <v>4379.132953670392</v>
       </c>
       <c r="F2" t="n">
-        <v>291.4720379828158</v>
+        <v>62.67471693647087</v>
       </c>
       <c r="G2" t="n">
-        <v>399.51401657956</v>
+        <v>-693.7961719112119</v>
       </c>
     </row>
     <row r="3">
@@ -1006,19 +980,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3412.584084342094</v>
+        <v>1423.008200860332</v>
       </c>
       <c r="E3" t="n">
-        <v>4052.019425827441</v>
+        <v>2161.007449441295</v>
       </c>
       <c r="F3" t="n">
-        <v>344.2652053443095</v>
+        <v>51.29597042390506</v>
       </c>
       <c r="G3" t="n">
-        <v>273.9178198574245</v>
+        <v>-413.941742450112</v>
       </c>
     </row>
     <row r="4">
@@ -1033,19 +1007,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3237.288670627624</v>
+        <v>1419.616149953374</v>
       </c>
       <c r="E4" t="n">
-        <v>3899.536969852353</v>
+        <v>2075.325207428116</v>
       </c>
       <c r="F4" t="n">
-        <v>308.1099700890248</v>
+        <v>58.30086866338702</v>
       </c>
       <c r="G4" t="n">
-        <v>228.3805735501638</v>
+        <v>-310.3226728332162</v>
       </c>
     </row>
   </sheetData>
@@ -1121,19 +1095,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>6085.555116977496</v>
+        <v>2945.770059569986</v>
       </c>
       <c r="F2" t="n">
-        <v>7469.276705990821</v>
+        <v>4379.132953670392</v>
       </c>
       <c r="G2" t="n">
-        <v>291.4720379828158</v>
+        <v>62.67471693647087</v>
       </c>
       <c r="H2" t="n">
-        <v>399.51401657956</v>
+        <v>-693.7961719112119</v>
       </c>
     </row>
     <row r="3">
@@ -1153,19 +1127,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3412.584084342094</v>
+        <v>1423.008200860332</v>
       </c>
       <c r="F3" t="n">
-        <v>4052.019425827441</v>
+        <v>2161.007449441295</v>
       </c>
       <c r="G3" t="n">
-        <v>344.2652053443095</v>
+        <v>51.29597042390506</v>
       </c>
       <c r="H3" t="n">
-        <v>273.9178198574245</v>
+        <v>-413.941742450112</v>
       </c>
     </row>
     <row r="4">
@@ -1185,19 +1159,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>3237.288670627624</v>
+        <v>1419.616149953374</v>
       </c>
       <c r="F4" t="n">
-        <v>3899.536969852353</v>
+        <v>2075.325207428116</v>
       </c>
       <c r="G4" t="n">
-        <v>308.1099700890248</v>
+        <v>58.30086866338702</v>
       </c>
       <c r="H4" t="n">
-        <v>228.3805735501638</v>
+        <v>-310.3226728332162</v>
       </c>
     </row>
   </sheetData>

--- a/release_1_0_0/data/files/output/ml/eval_ml_loo.xlsx
+++ b/release_1_0_0/data/files/output/ml/eval_ml_loo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,77 +456,107 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>ml_tc_sim_v2__montant_ventes_par_mois</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pred_sim_v2_brut__montant_ventes_par_mois</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>montant_ventes_par_mois_reel</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>montant_ventes_par_mois_predit</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>montant_ventes_par_mois_erreur</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>montant_ventes_par_mois_erreur_absolue</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>pred_sim_v2__montant_ventes_par_mois</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pred_ml_tc_sim_v2__montant_ventes_par_mois</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>montant_marge_par_mois_reel</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>montant_marge_par_mois_predit</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>montant_marge_par_mois_erreur</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>montant_marge_par_mois_erreur_absolue</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pred_sim_v2__montant_marge_par_mois</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>pred_ml_tc_sim_v2__montant_marge_par_mois</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_par_mois_reel</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_par_mois_predit</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_par_mois_erreur</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>montant_marge_selon_coef_par_mois_erreur_absolue</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pred_sim_v2__montant_marge_selon_coef_par_mois</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pred_ml_tc_sim_v2__montant_marge_selon_coef_par_mois</t>
         </is>
       </c>
     </row>
@@ -548,58 +578,78 @@
         <v>0.04412064830175411</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0719614252448082</v>
+        <v>0.06503652036190033</v>
       </c>
       <c r="F2" t="n">
         <v>0.09885716389404486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7279333374558112</v>
+        <v>0.6578837364948734</v>
       </c>
       <c r="H2" t="n">
+        <v>7607.705095151479</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11563.90509922685</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ml_tc→ml_tc_sim_v2→ml_ca</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>3432.306971428518</v>
       </c>
-      <c r="I2" t="n">
-        <v>8417.752032902474</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4985.445061473956</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4985.445061473956</v>
-      </c>
       <c r="L2" t="n">
+        <v>11241.8544921875</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7809.547520758983</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7809.547520758983</v>
+      </c>
+      <c r="O2" t="n">
         <v>11563.90509922685</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
+        <v>7607.705095151479</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2214.074874999865</v>
       </c>
-      <c r="N2" t="n">
-        <v>4410.475510040579</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2196.400635040714</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2196.400635040714</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
+        <v>5890.162092139533</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3676.087217139668</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3676.087217139668</v>
+      </c>
+      <c r="U2" t="n">
         <v>6058.900290863949</v>
       </c>
-      <c r="R2" t="n">
+      <c r="V2" t="n">
+        <v>3986.05196240345</v>
+      </c>
+      <c r="W2" t="n">
         <v>1977.989434346401</v>
       </c>
-      <c r="S2" t="n">
-        <v>4417.128453020146</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2439.139018673745</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2439.139018673745</v>
-      </c>
-      <c r="V2" t="n">
-        <v>6068.039785701236</v>
+      <c r="X2" t="n">
+        <v>5899.04705532552</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3921.057620979119</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3921.057620979119</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6068.039785701235</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3992.06468741668</v>
       </c>
     </row>
     <row r="3">
@@ -620,58 +670,78 @@
         <v>0.03407324952031283</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03405093401670456</v>
+        <v>0.0339326411485672</v>
       </c>
       <c r="F3" t="n">
         <v>0.03067157265002578</v>
       </c>
       <c r="G3" t="n">
-        <v>1.110178940129304</v>
+        <v>1.106322180989917</v>
       </c>
       <c r="H3" t="n">
+        <v>706.4473430627784</v>
+      </c>
+      <c r="I3" t="n">
+        <v>638.5548036564379</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ml_tc→ml_tc_sim_v2→ml_ca</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>570.2660606060817</v>
       </c>
-      <c r="I3" t="n">
-        <v>708.9100951377798</v>
-      </c>
-      <c r="J3" t="n">
-        <v>138.644034531698</v>
-      </c>
-      <c r="K3" t="n">
-        <v>138.644034531698</v>
-      </c>
       <c r="L3" t="n">
+        <v>570.2705078125</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.004447206418262795</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.004447206418262795</v>
+      </c>
+      <c r="O3" t="n">
         <v>638.5548036564379</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
+        <v>706.4473430627784</v>
+      </c>
+      <c r="Q3" t="n">
         <v>233.321212121201</v>
       </c>
-      <c r="N3" t="n">
-        <v>288.7385163979222</v>
-      </c>
-      <c r="O3" t="n">
-        <v>55.41730427672121</v>
-      </c>
-      <c r="P3" t="n">
-        <v>55.41730427672121</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
+        <v>232.2707230446038</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-1.050489076597245</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.050489076597245</v>
+      </c>
+      <c r="U3" t="n">
         <v>260.0828622855092</v>
       </c>
-      <c r="R3" t="n">
+      <c r="V3" t="n">
+        <v>287.7354394418047</v>
+      </c>
+      <c r="W3" t="n">
         <v>248.7434418642236</v>
       </c>
-      <c r="S3" t="n">
-        <v>305.1609112814566</v>
-      </c>
-      <c r="T3" t="n">
-        <v>56.41746941723298</v>
-      </c>
-      <c r="U3" t="n">
-        <v>56.41746941723298</v>
-      </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
+        <v>245.4814355650827</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-3.262006299140921</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.262006299140921</v>
+      </c>
+      <c r="AA3" t="n">
         <v>274.8754279611125</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>304.1007829624747</v>
       </c>
     </row>
     <row r="4">
@@ -692,58 +762,78 @@
         <v>0.107751341483961</v>
       </c>
       <c r="E4" t="n">
-        <v>0.044735137373209</v>
+        <v>0.04871275648474693</v>
       </c>
       <c r="F4" t="n">
         <v>0.0711871475801257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6284159275079357</v>
+        <v>0.6842914506430757</v>
       </c>
       <c r="H4" t="n">
+        <v>9490.743091663242</v>
+      </c>
+      <c r="I4" t="n">
+        <v>13869.445661997</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ml_tc→ml_tc_sim_v2→ml_ca</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>17096.63041667935</v>
       </c>
-      <c r="I4" t="n">
-        <v>8715.780559704761</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-8380.849856974592</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8380.849856974592</v>
-      </c>
       <c r="L4" t="n">
+        <v>2788.908447265625</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-14307.72196941373</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14307.72196941373</v>
+      </c>
+      <c r="O4" t="n">
         <v>13869.445661997</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
+        <v>9490.743091663242</v>
+      </c>
+      <c r="Q4" t="n">
         <v>9167.626249997114</v>
       </c>
-      <c r="N4" t="n">
-        <v>4883.449008895345</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-4284.177241101769</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4284.177241101769</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>7771.045887174265</v>
-      </c>
       <c r="R4" t="n">
+        <v>1562.624494662647</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-7605.001755334468</v>
+      </c>
+      <c r="T4" t="n">
+        <v>7605.001755334468</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7771.045887174266</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5317.660263148386</v>
+      </c>
+      <c r="W4" t="n">
         <v>8864.534661573482</v>
       </c>
-      <c r="S4" t="n">
-        <v>4948.110586258861</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-3916.42407531462</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3916.42407531462</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
+        <v>1583.315150891001</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-7281.21951068248</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7281.21951068248</v>
+      </c>
+      <c r="AA4" t="n">
         <v>7873.942033712021</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5388.071216528288</v>
       </c>
     </row>
     <row r="5">
@@ -764,58 +854,78 @@
         <v>0.01104139660255675</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01098483242094517</v>
+        <v>0.01075195986777544</v>
       </c>
       <c r="F5" t="n">
         <v>0.009647482529509114</v>
       </c>
       <c r="G5" t="n">
-        <v>1.138621644283413</v>
+        <v>1.114483476377181</v>
       </c>
       <c r="H5" t="n">
+        <v>2207.539268438208</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1980.773439202698</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ml_tc→ml_tc_sim_v2→ml_ca</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>1766.508730769235</v>
       </c>
-      <c r="I5" t="n">
-        <v>2272.354353910516</v>
-      </c>
-      <c r="J5" t="n">
-        <v>505.8456231412815</v>
-      </c>
-      <c r="K5" t="n">
-        <v>505.8456231412815</v>
-      </c>
       <c r="L5" t="n">
-        <v>1995.706269346929</v>
+        <v>1764.227905273438</v>
       </c>
       <c r="M5" t="n">
+        <v>-2.280825495797217</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.280825495797217</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1980.773439202698</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2207.539268438208</v>
+      </c>
+      <c r="Q5" t="n">
         <v>974.3293076923151</v>
       </c>
-      <c r="N5" t="n">
-        <v>1245.17751440043</v>
-      </c>
-      <c r="O5" t="n">
-        <v>270.848206708115</v>
-      </c>
-      <c r="P5" t="n">
-        <v>270.848206708115</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1093.583211466244</v>
-      </c>
       <c r="R5" t="n">
+        <v>976.9682365869352</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.638928894620108</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.638928894620108</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1096.883644222921</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1222.458696994833</v>
+      </c>
+      <c r="W5" t="n">
         <v>815.1594794547862</v>
       </c>
-      <c r="S5" t="n">
-        <v>1092.836684164202</v>
-      </c>
-      <c r="T5" t="n">
-        <v>277.6772047094159</v>
-      </c>
-      <c r="U5" t="n">
-        <v>277.6772047094159</v>
-      </c>
-      <c r="V5" t="n">
-        <v>959.7891359706011</v>
+      <c r="X5" t="n">
+        <v>807.9123727183238</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-7.247106736462342</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.247106736462342</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>907.0774610810031</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1010.922842168944</v>
       </c>
     </row>
     <row r="6">
@@ -836,58 +946,78 @@
         <v>0.1160233891551693</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03781047090888023</v>
+        <v>0.03666472434997559</v>
       </c>
       <c r="F6" t="n">
         <v>0.06723040242611222</v>
       </c>
       <c r="G6" t="n">
-        <v>0.562401377121531</v>
+        <v>0.5453592872699367</v>
       </c>
       <c r="H6" t="n">
+        <v>356.23074199858</v>
+      </c>
+      <c r="I6" t="n">
+        <v>653.2037691736537</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ml_tc→ml_tc_sim_v2→ml_ca</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>1085.428421052641</v>
       </c>
-      <c r="I6" t="n">
-        <v>367.3626993242375</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-718.0657217284032</v>
-      </c>
-      <c r="K6" t="n">
-        <v>718.0657217284032</v>
-      </c>
       <c r="L6" t="n">
+        <v>1303.063720703125</v>
+      </c>
+      <c r="M6" t="n">
+        <v>217.6352996504843</v>
+      </c>
+      <c r="N6" t="n">
+        <v>217.6352996504843</v>
+      </c>
+      <c r="O6" t="n">
         <v>653.2037691736537</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
+        <v>356.23074199858</v>
+      </c>
+      <c r="Q6" t="n">
         <v>522.3989473684123</v>
       </c>
-      <c r="N6" t="n">
-        <v>214.2013301940715</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-308.1976171743408</v>
-      </c>
-      <c r="P6" t="n">
-        <v>308.1976171743408</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
+        <v>759.7885762917194</v>
+      </c>
+      <c r="S6" t="n">
+        <v>237.3896289233071</v>
+      </c>
+      <c r="T6" t="n">
+        <v>237.3896289233071</v>
+      </c>
+      <c r="U6" t="n">
         <v>380.8691424092727</v>
       </c>
-      <c r="R6" t="n">
+      <c r="V6" t="n">
+        <v>207.710524047433</v>
+      </c>
+      <c r="W6" t="n">
         <v>607.1911078395337</v>
       </c>
-      <c r="S6" t="n">
-        <v>198.7681261876786</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-408.4229816518551</v>
-      </c>
-      <c r="U6" t="n">
-        <v>408.4229816518551</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
+        <v>705.0458158755592</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>97.8547080360255</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>97.8547080360255</v>
+      </c>
+      <c r="AA6" t="n">
         <v>353.4275239598608</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>192.7449825683282</v>
       </c>
     </row>
   </sheetData>
@@ -901,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,82 +1074,109 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>montant_ventes_par_mois</t>
+          <t>taux_conversion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Montant des ventes mensuel</t>
+          <t>Taux de conversion (ml_tc)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2945.770059569986</v>
+        <v>0.03194863339421618</v>
       </c>
       <c r="E2" t="n">
-        <v>4379.132953670392</v>
+        <v>0.04521267399025757</v>
       </c>
       <c r="F2" t="n">
-        <v>62.67471693647087</v>
+        <v>34.72609737086304</v>
       </c>
       <c r="G2" t="n">
-        <v>-693.7961719112119</v>
+        <v>-0.0235822845701577</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>montant_marge_par_mois</t>
+          <t>montant_ventes_par_mois</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marge mensuelle selon prix marche</t>
+          <t>Montant des ventes mensuel</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1423.008200860332</v>
+        <v>4467.438012505081</v>
       </c>
       <c r="E3" t="n">
-        <v>2161.007449441295</v>
+        <v>7290.367765193683</v>
       </c>
       <c r="F3" t="n">
-        <v>51.29597042390506</v>
+        <v>66.2796954384</v>
       </c>
       <c r="G3" t="n">
-        <v>-413.941742450112</v>
+        <v>-1256.563105458728</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>montant_marge_selon_coef_par_mois</t>
+          <t>montant_marge_par_mois</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marge mensuelle selon coefficient fixe</t>
+          <t>Marge mensuelle selon prix marche</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1419.616149953374</v>
+        <v>2304.433603873732</v>
       </c>
       <c r="E4" t="n">
-        <v>2075.325207428116</v>
+        <v>3779.048314855246</v>
       </c>
       <c r="F4" t="n">
-        <v>58.30086866338702</v>
+        <v>59.03018241163142</v>
       </c>
       <c r="G4" t="n">
-        <v>-310.3226728332162</v>
+        <v>-737.987293890694</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>montant_marge_selon_coef_par_mois</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Marge mensuelle selon coefficient fixe</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2262.128190546645</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3698.661626451049</v>
+      </c>
+      <c r="F5" t="n">
+        <v>59.73793521139064</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-654.5632589405878</v>
       </c>
     </row>
   </sheetData>
@@ -1033,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,28 +1243,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>montant_ventes_par_mois</t>
+          <t>taux_conversion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Montant des ventes mensuel</t>
+          <t>Taux de conversion (ml_tc)</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2945.770059569986</v>
+        <v>0.03194863339421618</v>
       </c>
       <c r="F2" t="n">
-        <v>4379.132953670392</v>
+        <v>0.04521267399025757</v>
       </c>
       <c r="G2" t="n">
-        <v>62.67471693647087</v>
+        <v>34.72609737086304</v>
       </c>
       <c r="H2" t="n">
-        <v>-693.7961719112119</v>
+        <v>-0.0235822845701577</v>
       </c>
     </row>
     <row r="3">
@@ -1118,28 +1275,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>montant_marge_par_mois</t>
+          <t>montant_ventes_par_mois</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marge mensuelle selon prix marche</t>
+          <t>Montant des ventes mensuel</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1423.008200860332</v>
+        <v>4467.438012505081</v>
       </c>
       <c r="F3" t="n">
-        <v>2161.007449441295</v>
+        <v>7290.367765193683</v>
       </c>
       <c r="G3" t="n">
-        <v>51.29597042390506</v>
+        <v>66.2796954384</v>
       </c>
       <c r="H3" t="n">
-        <v>-413.941742450112</v>
+        <v>-1256.563105458728</v>
       </c>
     </row>
     <row r="4">
@@ -1150,28 +1307,60 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>montant_marge_selon_coef_par_mois</t>
+          <t>montant_marge_par_mois</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marge mensuelle selon coefficient fixe</t>
+          <t>Marge mensuelle selon prix marche</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1419.616149953374</v>
+        <v>2304.433603873732</v>
       </c>
       <c r="F4" t="n">
-        <v>2075.325207428116</v>
+        <v>3779.048314855246</v>
       </c>
       <c r="G4" t="n">
-        <v>58.30086866338702</v>
+        <v>59.03018241163142</v>
       </c>
       <c r="H4" t="n">
-        <v>-310.3226728332162</v>
+        <v>-737.987293890694</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>montant_marge_selon_coef_par_mois</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marge mensuelle selon coefficient fixe</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2262.128190546645</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3698.661626451049</v>
+      </c>
+      <c r="G5" t="n">
+        <v>59.73793521139064</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-654.5632589405878</v>
       </c>
     </row>
   </sheetData>
